--- a/output/Tables/7000 steps/DALY_prev_fraction_7000steps.xlsx
+++ b/output/Tables/7000 steps/DALY_prev_fraction_7000steps.xlsx
@@ -395,33 +395,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B3">
-        <v>-2.496960483206164</v>
+        <v>-2.381963188638068</v>
       </c>
       <c r="C3">
-        <v>-2.362838386555952</v>
+        <v>-2.250352265194579</v>
       </c>
       <c r="D3">
-        <v>-2.508959880310325</v>
+        <v>-2.392881600186491</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B4">
-        <v>-2.381963188638068</v>
+        <v>-2.496960483206164</v>
       </c>
       <c r="C4">
-        <v>-2.250352265194579</v>
+        <v>-2.362838386555952</v>
       </c>
       <c r="D4">
-        <v>-2.392881600186491</v>
+        <v>-2.508959880310325</v>
       </c>
     </row>
     <row r="5">
